--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="235">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -475,10 +475,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -3140,7 +3143,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>148</v>
       </c>
@@ -3153,13 +3156,13 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3170,8 +3173,12 @@
       <c r="K21" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="L21" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3241,10 +3248,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3258,7 +3265,7 @@
         <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>74</v>
@@ -3267,13 +3274,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3324,7 +3331,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3344,10 +3351,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3443,12 +3450,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3458,13 +3465,13 @@
         <v>62</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -3477,7 +3484,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3489,7 +3496,7 @@
         <v>74</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>74</v>
@@ -3528,7 +3535,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3546,28 +3553,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -3580,7 +3587,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3592,7 +3599,7 @@
         <v>74</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>74</v>
@@ -3631,7 +3638,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3651,17 +3658,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3683,7 +3690,7 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3695,7 +3702,7 @@
         <v>74</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>74</v>
@@ -3734,7 +3741,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3754,17 +3761,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -3786,7 +3793,7 @@
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3837,7 +3844,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3855,28 +3862,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -3889,7 +3896,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3901,7 +3908,7 @@
         <v>74</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>74</v>
@@ -3940,7 +3947,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3960,10 +3967,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3986,11 +3993,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4041,7 +4048,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4061,10 +4068,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4091,7 +4098,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4142,7 +4149,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4162,17 +4169,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4190,11 +4197,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4245,7 +4252,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4265,17 +4272,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4293,11 +4300,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4348,7 +4355,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4368,17 +4375,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4396,11 +4403,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4451,7 +4458,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4471,10 +4478,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4488,7 +4495,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4497,13 +4504,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4554,7 +4561,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4574,10 +4581,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4591,7 +4598,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4600,13 +4607,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4657,7 +4664,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4677,10 +4684,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4703,7 +4710,7 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -4756,7 +4763,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4776,10 +4783,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4835,25 +4842,25 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4873,10 +4880,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4899,7 +4906,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -4952,7 +4959,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4972,10 +4979,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4998,7 +5005,7 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -5051,7 +5058,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5071,10 +5078,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5097,7 +5104,7 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
@@ -5150,7 +5157,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5170,10 +5177,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5196,7 +5203,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -5249,7 +5256,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5269,10 +5276,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5295,7 +5302,7 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -5348,7 +5355,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5368,10 +5375,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5469,10 +5476,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5570,10 +5577,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5671,10 +5678,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5772,10 +5779,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5875,10 +5882,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5978,10 +5985,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6081,10 +6088,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6184,10 +6191,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6285,10 +6292,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6315,7 +6322,7 @@
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6324,7 +6331,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>74</v>
@@ -6366,7 +6373,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6386,10 +6393,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6423,49 +6430,49 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6485,10 +6492,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6511,7 +6518,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6564,7 +6571,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-points-de-vigilances-non-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
